--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/OREGON_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/OREGON_2019.xlsx
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C196">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C686">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C723">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C727">
@@ -20911,7 +20911,7 @@
         <v>82</v>
       </c>
       <c r="D1142">
-        <v>0.009166107757657053</v>
+        <v>0.009166107757657051</v>
       </c>
     </row>
     <row r="1143">
